--- a/daily_matches/job_matches_2026-07-27.xlsx
+++ b/daily_matches/job_matches_2026-07-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Specialist - Data Sciences</t>
+          <t>Data Scientist (Insurance Product)-Senior Associate</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>11.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Hugging Face, FAISS, ChromaDB, S3, EC2, FastAPI, Docker</t>
+          <t>Data Scientist, RAG, Git, Tableau, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,112 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=044e306510bc50a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Power BI, SQL</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f495df65f464e1ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Cloud DevSecOps Engineer</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Regions Financial</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=71ba8e5763807003</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>MyFitnessPal</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=17d62d43e9e7cb3c</t>
+          <t>https://www.indeed.com/viewjob?jk=1cce59b9e89e4a03</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-27.xlsx
+++ b/daily_matches/job_matches_2026-07-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,105 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Scientist (Insurance Product)-Senior Associate</t>
+          <t>Middleware Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Navat Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, EC2, Docker, CI/CD, Jenkins, GitHub Actions, Git, R</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84c495ca2a0cc395</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Data Engineer (AI/ML) III - 6253</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>itD Tech</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Redmond, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>11.1</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Tableau, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1cce59b9e89e4a03</t>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RAG, PyTorch, CI/CD, Git, Tableau, Matplotlib, Python, R, Scala, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1081434668904e99</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Senior Systems Software Engineer, Developer Productivity and Cloud Automation - GeForce NOW</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=597059b1cca79e48</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-27.xlsx
+++ b/daily_matches/job_matches_2026-07-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Middleware Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Navat Technologies Pvt Ltd</t>
+          <t>Enable Data</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.3</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Docker, CI/CD, Jenkins, GitHub Actions, Git, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, XGBoost, LightGBM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c495ca2a0cc395</t>
+          <t>https://www.indeed.com/viewjob?jk=08b279ac901c3356</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer (AI/ML) III - 6253</t>
+          <t>AI DevOps Engineer – 1099 Contract</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>itD Tech</t>
+          <t>Bitcot Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, PyTorch, CI/CD, Git, Tableau, Matplotlib, Python, R, Scala, Hypothesis Testing</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, Prompt Engineering, MLflow, Docker, Kubernetes, AKS, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,42 +531,532 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1081434668904e99</t>
+          <t>https://www.indeed.com/viewjob?jk=56400bd32a7b810d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Systems Software Engineer, Developer Productivity and Cloud Automation - GeForce NOW</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks, Kafka, MongoDB</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ad2d81d6d9a2d31</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Data Engineer - AI, Hybrid</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Research Triangle Park, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Snowflake, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6fb8abff88ebbaf0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Meijer</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, NLTK, Azure ML, Synapse, Git, Databricks, PySpark, Python</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0d564a81523cfbe</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Data Scientist with QuickSight</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tricon Solutions</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D7" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, S3, Redshift, Redshift, Quicksight, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0cafa2687175602</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AI Engineer - Senior</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Naples, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=494fde9edc0ba23a</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AWS Cloud Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Arkatechture</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, CI/CD, GitHub Actions, Terraform, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3391e6126aa7cb2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Marketing AI Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sonar</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Gemini, Copilot, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8917dd59da265b6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Forward Deployed AI Engineer (GenAI, AWS)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Provectus</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59d1f10b08a4a244</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Fort Meade, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>FastAPI, Docker, CI/CD, Git, MySQL, MongoDB, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a68b32f92addec92</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AI / Snowflake Cortex ML Analyst</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Smart Tech Skills LLC</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Cortex, CI/CD, Git, Snowflake, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12de521186863ea9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Quality Assurance Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AssetWatch</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>10</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=597059b1cca79e48</t>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80096f03945d5406</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Cyber Security Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Honeywell</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Jenkins, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ebb0beb94ca5185</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Hybrid-Cloud Systems Engineer III</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Port of Portland</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b457c8819912ff2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ultralytics LLC</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>PyTorch, OpenCV, YOLO, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6eed63dd4227b66</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ultralytics LLC</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PyTorch, OpenCV, YOLO, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a59d1d2d806cd822</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-27.xlsx
+++ b/daily_matches/job_matches_2026-07-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08b279ac901c3356</t>
+          <t>https://www.indeed.com/viewjob?jk=aed5867cc295ca6e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer – 1099 Contract</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bitcot Technologies Pvt Ltd</t>
+          <t>PLACE Corporate Careers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>23.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, Prompt Engineering, MLflow, Docker, Kubernetes, AKS, CI/CD</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, LightGBM, CatBoost</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56400bd32a7b810d</t>
+          <t>https://www.indeed.com/viewjob?jk=94d6622d48d77919</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>22.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks, Kafka, MongoDB</t>
+          <t>Machine Learning Engineer, LangChain, RAG, Copilot, Hugging Face, Pinecone, Prompt Engineering, PyTorch, S3, MLflow</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad2d81d6d9a2d31</t>
+          <t>https://www.indeed.com/viewjob?jk=d862011310c4cf0f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer - AI, Hybrid</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Snowflake, Python, SQL, R, Java</t>
+          <t>AI Engineer, RAG, Prompt Engineering, Data Lake, FastAPI, Kubernetes, AKS, CI/CD, Terraform, Databricks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fb8abff88ebbaf0</t>
+          <t>https://www.indeed.com/viewjob?jk=1c0930580a5bcd07</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Associate Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Meijer</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, NLTK, Azure ML, Synapse, Git, Databricks, PySpark, Python</t>
+          <t>Generative AI, RAG, Gemini, TensorFlow, BigQuery, Dataflow, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d564a81523cfbe</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad10bcc1b9c0d99</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist with QuickSight</t>
+          <t>Hadoop Big Data Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tricon Solutions</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, S3, Redshift, Redshift, Quicksight, Python, SQL</t>
+          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0cafa2687175602</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1ee56096500177</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Engineer - Senior</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Naples, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>RAG, S3, EC2, Glue, Redshift, Kinesis, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494fde9edc0ba23a</t>
+          <t>https://www.indeed.com/viewjob?jk=c844b36a2e1bda08</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AWS Cloud Infrastructure Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Arkatechture</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, CI/CD, GitHub Actions, Terraform, Git, R, Scala</t>
+          <t>LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3391e6126aa7cb2b</t>
+          <t>https://www.indeed.com/viewjob?jk=1155785404399fad</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marketing AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sonar</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Gemini, Copilot, Git, Python, R, Java, Scala</t>
+          <t>RAG, Mistral, Pinecone, Prompt Engineering, S3, FastAPI, CI/CD, Git, PostgreSQL, Matplotlib</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8917dd59da265b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=82fe4e268dbb7b66</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Forward Deployed AI Engineer (GenAI, AWS)</t>
+          <t>Senior AI Full stack Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
+          <t>LangChain, RAG, LLaMA, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d1f10b08a4a244</t>
+          <t>https://www.indeed.com/viewjob?jk=ea79db343d1443d7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>AWS DevOps Datadog</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, CI/CD, Git, MySQL, MongoDB, Python, SQL, R, Java</t>
+          <t>Generative AI, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a68b32f92addec92</t>
+          <t>https://www.indeed.com/viewjob?jk=fe2c3bc322ffddc5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI / Snowflake Cortex ML Analyst</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Cortex, CI/CD, Git, Snowflake, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12de521186863ea9</t>
+          <t>https://www.indeed.com/viewjob?jk=ff539c3ae99f7727</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Software Engineer (Financial Technology Platform) – Remote, Part-Time</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AssetWatch</t>
+          <t>QSentia</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Scala</t>
+          <t>AI Engineer, RAG, Gemini, FastAPI, Docker, CI/CD, Git, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80096f03945d5406</t>
+          <t>https://www.indeed.com/viewjob?jk=c058732107d6b9eb</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Cyber Security Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Jenkins, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
+          <t>RAG, Synapse, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ebb0beb94ca5185</t>
+          <t>https://www.indeed.com/viewjob?jk=0c0763ad74d36902</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Hybrid-Cloud Systems Engineer III</t>
+          <t>Applied AI Researcher</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Port of Portland</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, MLflow, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b457c8819912ff2</t>
+          <t>https://www.indeed.com/viewjob?jk=e0cdfb05b5e20bbe</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Applied AI Researcher</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ultralytics LLC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PyTorch, OpenCV, YOLO, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+          <t>AI Engineer, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, MLflow, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,42 +1021,987 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6eed63dd4227b66</t>
+          <t>https://www.indeed.com/viewjob?jk=7ff1e8306f86b3ad</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ultralytics LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0ffc09421c310dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>OCI Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MySQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=961c1329ccf392e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Data Scientist I</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Preferred Travel Group</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Snowflake, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c9e382eb24d5fdb0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AI Engineer III</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Vericast</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, S3, Kubernetes, CI/CD, Databricks, PySpark, SQL</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc2a0a88a6bb4e38</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AWS Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Global Information Technology</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3290810ec0e24d4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Architecture AI Co-op</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Copilot, FastAPI, Docker, CI/CD, Git, Python</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=803d9dafde5813a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data Platform Architect</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5bf583c77e4c9d72</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Azure Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc792ea130a24f8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>GenAI Platform / Engineering – Architecture</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Recluta Technologies</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Buffalo, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, FAISS, Pinecone, Prompt Engineering, Python</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f232ce072a45a1d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Python/Typescript</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SpotOn</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d2a0c037ae5b9a51</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Python/Typescript</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SpotOn</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>New York, NY, US USA</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D28" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eae7a451b8eab5c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Python/Typescript</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SpotOn</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1db872f0c3fcbaeb</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Python/Typescript</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SpotOn</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Royal Oak, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=635eaa8372f65390</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Python/Typescript</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SpotOn</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97c8ae17d4faca49</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Duetto Research</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Jenkins, GitHub Actions, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c724067b623b57d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Sr. Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Blue Yonder</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, FastAPI, Python, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=545d722708049a80</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior .NET Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2a6f257a33bda0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>QA Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=961339fe618c4f4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Kafka Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0f1f7ac1d6409a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Salesforce Development Engineer III</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>GM Financial</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Arlington, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, Terraform, Git, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e4b298a9510a69c</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SecDevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Knox Systems</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88be494da601a299</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Morningstar</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Kinesis, CI/CD, Kafka, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1cdec10064cec8d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>OpenShift Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
         <v>10</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>PyTorch, OpenCV, YOLO, Docker, Kubernetes, CI/CD, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a59d1d2d806cd822</t>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42cffb5d56f9eeaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, GenAI Technology</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Point72</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0edc640a4a625ed2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Logicbroker, Inc.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=32a02407366a3e1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>QA Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35e39b28e07e0e54</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior QA Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Morningstar</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7449bbd8c4ea6d5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Developer I</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>AMETEK</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1acc3919a08631c7</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-27.xlsx
+++ b/daily_matches/job_matches_2026-07-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Glue, FastAPI, CI/CD, Terraform, Git, PySpark, Kafka</t>
+          <t>Data Scientist, RAG, S3, EC2, Glue, Athena, Redshift, Data Lake, Kinesis, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f88f3978f6e2de83</t>
+          <t>https://www.indeed.com/viewjob?jk=20e8b241f5073b73</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr AI/Agentic Engineer</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lendistry</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>24.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Pinecone, Prompt Engineering, Docker</t>
+          <t>Data Scientist, RAG, S3, EC2, Glue, Athena, Redshift, Data Lake, Kinesis, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dae8f97fcffc564</t>
+          <t>https://www.indeed.com/viewjob?jk=9a43d246f182c799</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr AI/Agentic Engineer</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lendistry</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>24.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Pinecone, Prompt Engineering, Docker</t>
+          <t>Data Scientist, RAG, S3, EC2, Glue, Athena, Redshift, Data Lake, Kinesis, Kubernetes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b35ee771643085f0</t>
+          <t>https://www.indeed.com/viewjob?jk=75897b83126c3579</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr AI/Agentic Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lendistry</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>21.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Pinecone, Prompt Engineering, Docker</t>
+          <t>RAG, Copilot, S3, EC2, Glue, Athena, Docker, Kubernetes, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da58fa5e526275b7</t>
+          <t>https://www.indeed.com/viewjob?jk=c4430f4f7148ec3b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr AI/Agentic Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lendistry</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Pinecone, Prompt Engineering, Docker</t>
+          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1db565d51c86aed</t>
+          <t>https://www.indeed.com/viewjob?jk=84fb98656d187561</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr AI/Agentic Engineer</t>
+          <t>Senior Specialist - Data Sciences</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lendistry</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Pinecone, Prompt Engineering, Docker</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, TensorFlow, PyTorch, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b82724b7787ff26</t>
+          <t>https://www.indeed.com/viewjob?jk=39160aed3d43d707</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jazwares</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Docker, CI/CD, Terraform, Git, PostgreSQL, Python</t>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7985331f140b0ede</t>
+          <t>https://www.indeed.com/viewjob?jk=604235ed7d4b4875</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI Developer</t>
+          <t>Principle Data &amp; IT Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>OxyChem</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, S3, Docker, CI/CD, Git</t>
+          <t>RAG, CI/CD, Terraform, Git, PySpark, NoSQL, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77098ecf48edec11</t>
+          <t>https://www.indeed.com/viewjob?jk=aafa6193d63da13a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Associate Consultant, Generative AI</t>
+          <t>Machine Learning Engineer, Underwriting</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SIA</t>
+          <t>FloatMe</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, Docker, CI/CD</t>
+          <t>Machine Learning Engineer, Copilot, PyTorch, XGBoost, LightGBM, Git, Snowflake, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9b344b051cddd9</t>
+          <t>https://www.indeed.com/viewjob?jk=05dbeb64d9749da6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Development Engineer III (Backend + AI)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Subsplash</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Glue, Athena, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Prompt Engineering, S3, Docker, Kubernetes, Git, MySQL, MongoDB, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf6ee00929d1c54</t>
+          <t>https://www.indeed.com/viewjob?jk=dbaac11a2b43cf73</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Development Engineer III (Backend + AI)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Subsplash</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Glue, Athena, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Prompt Engineering, S3, Docker, Kubernetes, Git, MySQL, MongoDB, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e729f2a707e926b3</t>
+          <t>https://www.indeed.com/viewjob?jk=a85e8f380d2e7c95</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS, Enterprise IAM</t>
+          <t>Software Development Engineer III (Backend + AI)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Subsplash</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+          <t>RAG, Prompt Engineering, S3, Docker, Kubernetes, Git, MySQL, MongoDB, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eac59fd94e904980</t>
+          <t>https://www.indeed.com/viewjob?jk=8c616edca764e62f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Software Development Engineer III (Backend + AI)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Subsplash</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, SQL, R</t>
+          <t>RAG, Prompt Engineering, S3, Docker, Kubernetes, Git, MySQL, MongoDB, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5322c0e396d0bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=89ffba5b7d67e433</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Scientist, eCommerce Analytics</t>
+          <t>Software Development Engineer III (Backend + AI)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Subsplash</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
+          <t>RAG, Prompt Engineering, S3, Docker, Kubernetes, Git, MySQL, MongoDB, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dab152066bcc0fe2</t>
+          <t>https://www.indeed.com/viewjob?jk=b4e8750734805246</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Managed Kubernetes &amp; Slurm</t>
+          <t>Senior Quality Assurance (QA) Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lightning AI</t>
+          <t>Beck's Hybrids</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, IN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, PyTorch, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d038a26554fa6431</t>
+          <t>https://www.indeed.com/viewjob?jk=42f536ef71f672fc</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Managed Kubernetes &amp; Slurm</t>
+          <t>Senior Security Automation &amp; SOAR Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lightning AI</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, PyTorch, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Docker, AKS, CI/CD, Jenkins, Terraform, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72355f1bc27606e4</t>
+          <t>https://www.indeed.com/viewjob?jk=945bfa278c31dac2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Test Automation Engineer - Agentic AI</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wolters Kluwer</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Coppell, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>RAG, Prompt Engineering, Terraform, Git, NoSQL, Python, SQL, R, Java, A/B Testing</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b36b2d438d15ce4</t>
+          <t>https://www.indeed.com/viewjob?jk=7b69514768f6a6aa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BI Data Engineer II</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Boston Beer Company</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, CI/CD, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Prompt Engineering, Terraform, Git, NoSQL, Python, SQL, R, Java, A/B Testing</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,19 +1091,19 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62785c4010471f7c</t>
+          <t>https://www.indeed.com/viewjob?jk=d18561a8a348533a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1112,21 +1112,581 @@
         </is>
       </c>
       <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Terraform, Git, NoSQL, Python, SQL, R, Java, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08a63ff87c905db9</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>innoVet Health, LLC</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Kinesis, Git, Databricks, PySpark, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c29f94189cd7da4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Analyst, GTM Analytics</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Palo Alto Networks</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, BigQuery, Git, BigQuery, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b35e09f799e5f66f</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Snowflake, Kafka, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ff16008b78c40ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Snowflake, Kafka, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c3f08d70fed55ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer (Eng - Senior) Cementing</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Halliburton</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, CI/CD, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1a4d58017fb2448</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Growth</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, EC2, Docker, Kubernetes, R, Java, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=caf28d93f5ff352b</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Software Engineer 2- Kiewit Technology Group</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kiewit Corporation</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Snowflake, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e16ff09aa0b39352</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Advisor, Agentic AI Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Eli Lilly</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Pinecone, PyTorch, CI/CD, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d87166a8de16dd74</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Platform Architect</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FullSteam LLC</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39f4427a39391996</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Hologic</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Marlborough, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Prompt Engineering, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da282858849b7db2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Hologic</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Prompt Engineering, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f7b1177ddfb7e56b</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Chargie</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Culver City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>10</v>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e8790b4247293910</t>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, Jenkins, Power BI, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da930629a1994ea8</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, ML Workflows - Weights &amp; Biases</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Weights &amp; Biases</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Git, Snowflake, Kafka, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04774e1c752664a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, ML Workflows - Weights &amp; Biases</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Weights &amp; Biases</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Git, Snowflake, Kafka, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a203618ee18b5cf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Software Engineer, Backend, Level 4</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce949e2a18f3e167</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer II</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CLEAR</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, AWS SageMaker, MLflow, AKS, Git, Snowflake, Python, R</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8679fc4a333470d9</t>
         </is>
       </c>
     </row>
